--- a/test/res/typedef.xlsx
+++ b/test/res/typedef.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A294D23B-55ED-F440-BFA3-DFF7AE4C064C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68711C61-A5E7-974F-8FBB-C3AB25D5F8DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17680" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="typedef" sheetId="2" r:id="rId1"/>
     <sheet name="main" sheetId="9" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">typedef!$A$2:$F$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">typedef!$A$2:$F$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -897,7 +897,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="55">
   <si>
     <t>id</t>
   </si>
@@ -1031,7 +1031,37 @@
     <t>{kind:"collect_coin",count:1,id:71001,duration:2}</t>
   </si>
   <si>
-    <t>{kind:"kill_monster",count: 1,id:5}</t>
+    <t>MonsterTeam</t>
+  </si>
+  <si>
+    <t>怪物队伍</t>
+  </si>
+  <si>
+    <t>leader</t>
+  </si>
+  <si>
+    <t>soldiers</t>
+  </si>
+  <si>
+    <t>int[]?</t>
+  </si>
+  <si>
+    <t>队长</t>
+  </si>
+  <si>
+    <t>成员</t>
+  </si>
+  <si>
+    <t>team</t>
+  </si>
+  <si>
+    <t>队伍</t>
+  </si>
+  <si>
+    <t>{kind:"kill_monster",count: 1,id:5, team: {leader: 1}}</t>
+  </si>
+  <si>
+    <t>MonsterTeam?</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1728,38 +1758,38 @@
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="B10" s="5"/>
       <c r="C10" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="16">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="C11" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="16">
@@ -1768,93 +1798,125 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="16">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="16">
       <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="16">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="16">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="16">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" ht="16">
-      <c r="A15" s="1"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6" ht="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" ht="16">
-      <c r="A17" s="1"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="16">
       <c r="A18" s="1"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" ht="16">
       <c r="A19" s="1"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="16">
       <c r="A20" s="1"/>
@@ -1874,27 +1936,27 @@
     </row>
     <row r="22" spans="1:6" ht="16">
       <c r="A22" s="1"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="8"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" ht="16">
       <c r="A23" s="1"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="8"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" ht="16">
       <c r="A24" s="1"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="8"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" ht="16">
       <c r="A25" s="1"/>
@@ -1911,6 +1973,30 @@
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="16">
+      <c r="A27" s="1"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="8"/>
+    </row>
+    <row r="28" spans="1:6" ht="16">
+      <c r="A28" s="1"/>
+      <c r="B28" s="7"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" ht="16">
+      <c r="A29" s="1"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1928,7 +2014,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="12" customFormat="1" ht="16">
@@ -2008,7 +2094,7 @@
         <v>41</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="12" customFormat="1" ht="16">
